--- a/rules/sources/sec.submissions.company/MAPPING.xlsx
+++ b/rules/sources/sec.submissions.company/MAPPING.xlsx
@@ -1161,13 +1161,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="62" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1183,10 +1184,15 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>When it is missing</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>When it fails</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Rules path</t>
         </is>
@@ -1205,10 +1211,15 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>The value is filled</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
           <t>Exception: the record never merges and never stops the run; fix or ignore it</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>quality.sec.submissions.company.v1.checks[0]</t>
         </is>
@@ -1358,7 +1369,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>A copy for matching only: upper case, USPS street words, no suite, 5-digit ZIP</t>
+          <t>Keeps a copy for matching only: upper case, USPS street words, no suite, 5-digit ZIP</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1532,13 +1543,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="43" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="43" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1549,15 +1561,20 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Dataset</t>
+          <t>MDM field</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Rank (1 wins)</t>
+          <t>Filled by, first wins</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Winner</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Rules path</t>
         </is>
@@ -1571,15 +1588,182 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>sec.submissions.company.v1</t>
+          <t>address</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>sec.submissions.company.v1, gleif.level1.v1</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>sec.submissions.company.v1</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>sec.submissions.company.v1</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>sec.submissions.company.v1</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>fiscal_year_end</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>sec.submissions.company.v1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>sec.submissions.company.v1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>sec.submissions.company.v1, gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>sec.submissions.company.v1</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>sic</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>sec.submissions.company.v1</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>sec.submissions.company.v1</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>sic_description</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>sec.submissions.company.v1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>sec.submissions.company.v1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>state_of_incorporation</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>sec.submissions.company.v1</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>sec.submissions.company.v1</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>merge/kinds/company.yaml defaults.sources</t>
         </is>
@@ -1643,7 +1827,7 @@
           <t>rules file comment</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1661,7 +1845,7 @@
           <t>rules file comment</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr"/>
+      <c r="D3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1679,7 +1863,7 @@
           <t>rules file comment</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1697,7 +1881,7 @@
           <t>rules file comment</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1715,7 +1899,7 @@
           <t>rules file comment</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1733,7 +1917,7 @@
           <t>rules file comment</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr"/>
+      <c r="D7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1751,7 +1935,7 @@
           <t>rules file comment</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1769,7 +1953,7 @@
           <t>rules file comment</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr"/>
+      <c r="D9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1787,7 +1971,7 @@
           <t>rules file comment</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr"/>
+      <c r="D10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1805,7 +1989,7 @@
           <t>rules file comment</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr"/>
+      <c r="D11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1823,7 +2007,7 @@
           <t>rules file comment</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr"/>
+      <c r="D12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1841,7 +2025,7 @@
           <t>rules file comment</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr"/>
+      <c r="D13" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/rules/sources/sec.submissions.company/MAPPING.xlsx
+++ b/rules/sources/sec.submissions.company/MAPPING.xlsx
@@ -1543,14 +1543,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="43" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="43" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1576,6 +1577,11 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Rule</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Rules path</t>
         </is>
       </c>
@@ -1603,6 +1609,11 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
           <t>merge/kinds/company.yaml defaults.sources</t>
         </is>
       </c>
@@ -1630,6 +1641,11 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
           <t>merge/kinds/company.yaml defaults.sources</t>
         </is>
       </c>
@@ -1657,6 +1673,11 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>merge/kinds/company.yaml defaults.sources</t>
         </is>
       </c>
@@ -1684,6 +1705,11 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>merge/kinds/company.yaml defaults.sources</t>
         </is>
       </c>
@@ -1711,6 +1737,11 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>merge/kinds/company.yaml defaults.sources</t>
         </is>
       </c>
@@ -1738,6 +1769,11 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>merge/kinds/company.yaml defaults.sources</t>
         </is>
       </c>
@@ -1764,6 +1800,11 @@
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>merge/kinds/company.yaml defaults.sources</t>
         </is>

--- a/rules/sources/sec.submissions.company/MAPPING.xlsx
+++ b/rules/sources/sec.submissions.company/MAPPING.xlsx
@@ -1548,7 +1548,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="43" customWidth="1" min="6" max="6"/>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>sec.submissions.company.v1, gleif.level1.v1</t>
+          <t>sec.submissions.company.v1, gleif.level1.v1, iapd.adv.filings.v1, iapd.adv.custody.v1</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>sec.submissions.company.v1, gleif.level1.v1</t>
+          <t>sec.submissions.company.v1, gleif.level1.v1, iapd.adv.filings.v1, iapd.adv.custody.v1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">

--- a/rules/sources/sec.submissions.company/MAPPING.xlsx
+++ b/rules/sources/sec.submissions.company/MAPPING.xlsx
@@ -1599,7 +1599,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>sec.submissions.company.v1, gleif.level1.v1, iapd.adv.filings.v1, iapd.adv.custody.v1</t>
+          <t>sec.submissions.company.v1, gleif.level1.v1, iapd.adv.filings.v1, iapd.adv.custodians.v1</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>sec.submissions.company.v1, gleif.level1.v1, iapd.adv.filings.v1, iapd.adv.custody.v1</t>
+          <t>sec.submissions.company.v1, gleif.level1.v1, iapd.adv.filings.v1, iapd.adv.custodians.v1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">

--- a/rules/sources/sec.submissions.company/MAPPING.xlsx
+++ b/rules/sources/sec.submissions.company/MAPPING.xlsx
@@ -1548,7 +1548,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="43" customWidth="1" min="6" max="6"/>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>sec.submissions.company.v1, gleif.level1.v1</t>
+          <t>sec.submissions.company.v1, gleif.level1.v1, iapd.adv.filings.v1, iapd.adv.custodians.v1</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>sec.submissions.company.v1, gleif.level1.v1</t>
+          <t>sec.submissions.company.v1, gleif.level1.v1, iapd.adv.filings.v1, iapd.adv.custodians.v1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">

--- a/rules/sources/sec.submissions.company/MAPPING.xlsx
+++ b/rules/sources/sec.submissions.company/MAPPING.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>mdm.sec.submissions.company.v1.contract.adapter.fields.name</t>
+          <t>mdm.sec.submissions.company.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.name</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>mdm.sec.submissions.company.v1.contract.adapter.fields.sic</t>
+          <t>mdm.sec.submissions.company.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.sic</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>mdm.sec.submissions.company.v1.contract.adapter.fields.sic_description</t>
+          <t>mdm.sec.submissions.company.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.sic_description</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>mdm.sec.submissions.company.v1.contract.adapter.fields.state_of_incorporation</t>
+          <t>mdm.sec.submissions.company.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.state_of_incorporation</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>mdm.sec.submissions.company.v1.contract.adapter.fields.fiscal_year_end</t>
+          <t>mdm.sec.submissions.company.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.fiscal_year_end</t>
         </is>
       </c>
     </row>
@@ -773,7 +773,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>mdm.sec.submissions.company.v1.contract.adapter.fields.description</t>
+          <t>mdm.sec.submissions.company.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.description</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>mdm.sec.submissions.company.v1.contract.adapter.fields.address</t>
+          <t>mdm.sec.submissions.company.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.address</t>
         </is>
       </c>
     </row>
@@ -837,7 +837,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>mdm.sec.submissions.company.v1.contract.adapter.fields.address</t>
+          <t>mdm.sec.submissions.company.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.address</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>mdm.sec.submissions.company.v1.contract.adapter.fields.address</t>
+          <t>mdm.sec.submissions.company.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.address</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>mdm.sec.submissions.company.v1.contract.adapter.fields.address</t>
+          <t>mdm.sec.submissions.company.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.address</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>mdm.sec.submissions.company.v1.contract.adapter.fields.address</t>
+          <t>mdm.sec.submissions.company.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.address</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>mdm.sec.submissions.company.v1.contract.adapter.fields.address</t>
+          <t>mdm.sec.submissions.company.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.address</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>mdm.sec.submissions.company.v1.contract.adapter.matching.business_postal_code</t>
+          <t>mdm.sec.submissions.company.v1.contract.adapter.reading.read.tables.mapped.columns.matching.object.fields.business_postal_code</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>mdm.sec.submissions.company.v1.contract.adapter.matching.business_country</t>
+          <t>mdm.sec.submissions.company.v1.contract.adapter.reading.read.tables.mapped.columns.matching.object.fields.business_country</t>
         </is>
       </c>
     </row>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>mdm.sec.submissions.company.v1.contract.adapter.matching.name_census</t>
+          <t>mdm.sec.submissions.company.v1.contract.adapter.reading.read.tables.mapped.columns.matching.object.fields.name_census</t>
         </is>
       </c>
     </row>

--- a/rules/sources/sec.submissions.company/MAPPING.xlsx
+++ b/rules/sources/sec.submissions.company/MAPPING.xlsx
@@ -1599,7 +1599,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>sec.submissions.company.v1, gleif.level1.v1, iapd.adv.filings.v1, iapd.adv.custodians.v1</t>
+          <t>sec.submissions.company.v1, gleif.level1.v1, iapd.adv.filings.v1, iapd.adv.custodians.v1, sec.nport.registrant.v1</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>sec.submissions.company.v1, gleif.level1.v1, iapd.adv.filings.v1, iapd.adv.custodians.v1</t>
+          <t>sec.submissions.company.v1, gleif.level1.v1, iapd.adv.filings.v1, iapd.adv.custodians.v1, sec.nport.registrant.v1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">

--- a/rules/sources/sec.submissions.company/MAPPING.xlsx
+++ b/rules/sources/sec.submissions.company/MAPPING.xlsx
@@ -566,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -673,13 +673,13 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>sic_description</t>
+          <t>state_of_incorporation</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>sic_description</t>
+          <t>state_of_incorporation</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>mdm.sec.submissions.company.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.sic_description</t>
+          <t>mdm.sec.submissions.company.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.state_of_incorporation</t>
         </is>
       </c>
     </row>
@@ -701,13 +701,13 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>state_of_incorporation</t>
+          <t>fiscal_year_end</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>state_of_incorporation</t>
+          <t>fiscal_year_end</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>mdm.sec.submissions.company.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.state_of_incorporation</t>
+          <t>mdm.sec.submissions.company.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.fiscal_year_end</t>
         </is>
       </c>
     </row>
@@ -729,13 +729,13 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>fiscal_year_end</t>
+          <t>description</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>fiscal_year_end</t>
+          <t>description</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>mdm.sec.submissions.company.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.fiscal_year_end</t>
+          <t>mdm.sec.submissions.company.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.description</t>
         </is>
       </c>
     </row>
@@ -757,13 +757,17 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr"/>
+          <t>address</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>street</t>
+        </is>
+      </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>business_address.street</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -773,7 +777,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>mdm.sec.submissions.company.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.description</t>
+          <t>mdm.sec.submissions.company.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.address</t>
         </is>
       </c>
     </row>
@@ -790,12 +794,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>street</t>
+          <t>street2</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>business_address.street</t>
+          <t>business_address.street2</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -822,12 +826,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>street2</t>
+          <t>city</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>business_address.street2</t>
+          <t>business_address.city</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -854,12 +858,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>region</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>business_address.city</t>
+          <t>business_address.region</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -886,12 +890,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>region</t>
+          <t>postcode</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>business_address.region</t>
+          <t>business_address.postal_code</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -918,12 +922,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>country</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>business_address.postal_code</t>
+          <t>business_address.country</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -945,27 +949,23 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>address</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>country</t>
-        </is>
-      </c>
+          <t>business_postal_code</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr"/>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>business_address.country</t>
+          <t>business_address.postal_code</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>MDM field</t>
+          <t>Matching only</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>mdm.sec.submissions.company.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.address</t>
+          <t>mdm.sec.submissions.company.v1.contract.adapter.reading.read.tables.mapped.columns.matching.object.fields.business_postal_code</t>
         </is>
       </c>
     </row>
@@ -977,13 +977,13 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>business_postal_code</t>
+          <t>business_country</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr"/>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>business_address.postal_code</t>
+          <t>business_address.country</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>mdm.sec.submissions.company.v1.contract.adapter.reading.read.tables.mapped.columns.matching.object.fields.business_postal_code</t>
+          <t>mdm.sec.submissions.company.v1.contract.adapter.reading.read.tables.mapped.columns.matching.object.fields.business_country</t>
         </is>
       </c>
     </row>
@@ -1005,13 +1005,13 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>business_country</t>
+          <t>name_census</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr"/>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>business_address.country</t>
+          <t>name_census</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1020,34 +1020,6 @@
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>mdm.sec.submissions.company.v1.contract.adapter.reading.read.tables.mapped.columns.matching.object.fields.business_country</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>sec.submissions.company.v1</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>name_census</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr"/>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>name_census</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Matching only</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>mdm.sec.submissions.company.v1.contract.adapter.reading.read.tables.mapped.columns.matching.object.fields.name_census</t>
         </is>
@@ -1543,7 +1515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1754,7 +1726,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>sic_description</t>
+          <t>state_of_incorporation</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1773,38 +1745,6 @@
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>merge/kinds/company.yaml defaults.sources</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>company</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>state_of_incorporation</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>sec.submissions.company.v1</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>sec.submissions.company.v1</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Kind default</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>merge/kinds/company.yaml defaults.sources</t>
         </is>

--- a/rules/sources/sec.submissions.company/MAPPING.xlsx
+++ b/rules/sources/sec.submissions.company/MAPPING.xlsx
@@ -13,7 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Critical data elements" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data quality" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Who wins" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pipeline targets" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pipeline steps" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1761,6 +1763,577 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="51" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="31" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Run checks</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Lease seconds</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Heartbeat seconds</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Rules path</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>capture</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>manifest.hash, work.accounting, journal.delivered</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>bookkeeping.targets.capture</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>mastering</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>manifest.hash, work.accounting, journal.delivered</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>bookkeeping.targets.mastering</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>mdm</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>manifest.hash, work.accounting, journal.delivered</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>bookkeeping.targets.mdm</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Operation</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Requires</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Leases</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Checks</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Rules path</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>capture</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>capture</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>artifact.copy</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>{artifact_id}</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>artifact:{destination}</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>input.hash, output.receipt</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>bookkeeping.targets.capture.steps[0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>mastering</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>source.read</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>{unit}</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>artifact:{destination}</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>input.hash, output.receipt, source.output</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>bookkeeping.targets.mastering.steps[0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>mastering</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>keys</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>source.read</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>{unit}</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>artifact:{destination}</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>input.hash, output.receipt, source.output</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>bookkeeping.targets.mastering.steps[1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>mastering</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>catalog</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>source.read</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>{unit}</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>artifact:{destination}</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>input.hash, output.receipt, source.output</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>bookkeeping.targets.mastering.steps[2]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>mastering</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>census</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>source.read</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>keys</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>{unit}</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>artifact:{destination}</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>input.hash, output.receipt, source.output</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>bookkeeping.targets.mastering.steps[3]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>mastering</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>combine</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>source.combine</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>main, catalog, census</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>{unit}</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>artifact:{destination}</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>input.hash, output.receipt, source.combined</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>bookkeeping.targets.mastering.steps[4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>mastering</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>records</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>mdm.prepare</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>combine</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>{unit}</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>artifact:{destination}</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>input.hash, output.receipt, mdm.prepared</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>bookkeeping.targets.mastering.steps[5]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>mastering</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>merge</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>mdm.merge</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>records</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>{batch_id}</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>mdm:consumer:{consumer}</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>input.hash, output.receipt, mdm.committed</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>bookkeeping.targets.mastering.steps[6]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>mastering</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>processed</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>journal.record</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>merge</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>{unit}</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>artifact:{destination}</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>input.hash, output.receipt, journal.recorded</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>bookkeeping.targets.mastering.steps[7]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>mdm</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>merge</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>mdm.merge</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr"/>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>{batch_id}</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>mdm:consumer:{consumer}</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>input.hash, output.receipt, mdm.committed</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>bookkeeping.targets.mdm.steps[0]</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
